--- a/research/traditional_assets/database/data/brazil/brazil_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_precious_metals.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,26 +587,8 @@
           <t>Precious Metals</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.09480000000000001</v>
-      </c>
-      <c r="G2">
-        <v>-162.2</v>
-      </c>
-      <c r="H2">
-        <v>-162.2</v>
-      </c>
-      <c r="I2">
-        <v>-340.3</v>
-      </c>
-      <c r="J2">
-        <v>-340.3</v>
-      </c>
       <c r="K2">
-        <v>-2.62</v>
-      </c>
-      <c r="L2">
-        <v>-262</v>
+        <v>-0.548</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,61 +612,46 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.0006038242200603823</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>0.08408602329195512</v>
-      </c>
-      <c r="Z2">
-        <v>-0.004537205081669692</v>
+        <v>0.1613807534905092</v>
       </c>
       <c r="AB2">
-        <v>0.08398916717181072</v>
+        <v>0.1613807534905092</v>
       </c>
       <c r="AD2">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>0.003276715260131069</v>
-      </c>
-      <c r="AI2">
-        <v>0.1888246628131021</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.002676480428236868</v>
-      </c>
-      <c r="AK2">
-        <v>0.1596806387225549</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>-0.02941176470588236</v>
-      </c>
-      <c r="AO2">
-        <v>-11.49662162162162</v>
+        <v>-0</v>
       </c>
       <c r="AP2">
-        <v>-0.02400960384153662</v>
-      </c>
-      <c r="AQ2">
-        <v>-11.49662162162162</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -695,7 +662,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brazil Minerals, Inc. (OTCPK:BMIX)</t>
+          <t>Jupiter Gold Corporation (OTCPK:JUPG.F)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -703,26 +670,8 @@
           <t>Precious Metals</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.09480000000000001</v>
-      </c>
-      <c r="G3">
-        <v>-123</v>
-      </c>
-      <c r="H3">
-        <v>-123</v>
-      </c>
-      <c r="I3">
-        <v>-299</v>
-      </c>
-      <c r="J3">
-        <v>-299</v>
-      </c>
       <c r="K3">
-        <v>-2.19</v>
-      </c>
-      <c r="L3">
-        <v>-219</v>
+        <v>-0.548</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,155 +695,45 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.0007627118644067796</v>
-      </c>
-      <c r="W3">
-        <v>0.6033057851239669</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.08418042816228374</v>
-      </c>
-      <c r="Y3">
-        <v>0.5191253569616832</v>
-      </c>
-      <c r="Z3">
-        <v>-0.004537205081669692</v>
-      </c>
-      <c r="AA3">
-        <v>1.356624319419238</v>
+        <v>0.1613807534905092</v>
       </c>
       <c r="AB3">
-        <v>0.08398671592199494</v>
-      </c>
-      <c r="AC3">
-        <v>1.272637603497243</v>
+        <v>0.1613807534905092</v>
       </c>
       <c r="AD3">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.004135370073423917</v>
-      </c>
-      <c r="AI3">
-        <v>0.1888246628131021</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.003378378378378379</v>
-      </c>
-      <c r="AK3">
-        <v>0.1596806387225549</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>-0.03333333333333333</v>
-      </c>
-      <c r="AO3">
-        <v>-10.10135135135135</v>
+        <v>-0</v>
       </c>
       <c r="AP3">
-        <v>-0.0272108843537415</v>
-      </c>
-      <c r="AQ3">
-        <v>-10.10135135135135</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Jupiter Gold Corporation (OTCPK:JUPG.F)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Precious Metals</t>
-        </is>
-      </c>
-      <c r="K4">
-        <v>-0.43</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0.0839916184216265</v>
-      </c>
-      <c r="AB4">
-        <v>0.0839916184216265</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>-0</v>
-      </c>
-      <c r="AP4">
         <v>-0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/brazil/brazil_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_precious_metals.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,8 +587,26 @@
           <t>Precious Metals</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.5679999999999999</v>
+      </c>
+      <c r="G2">
+        <v>-6134</v>
+      </c>
+      <c r="H2">
+        <v>-6134</v>
+      </c>
+      <c r="I2">
+        <v>-27457</v>
+      </c>
+      <c r="J2">
+        <v>-27457</v>
+      </c>
       <c r="K2">
-        <v>-0.548</v>
+        <v>-27.257</v>
+      </c>
+      <c r="L2">
+        <v>-27257</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,16 +630,19 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.06421580998850285</v>
       </c>
       <c r="X2">
-        <v>0.1613807534905092</v>
+        <v>0.1319741298819643</v>
+      </c>
+      <c r="Z2">
+        <v>0.001270648030495553</v>
       </c>
       <c r="AB2">
-        <v>0.1613807534905092</v>
+        <v>0.1319741298819643</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -633,13 +654,19 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>-22.9</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>-0.06862245662401487</v>
+      </c>
+      <c r="AK2">
+        <v>1.389563106796117</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -651,7 +678,7 @@
         <v>-0</v>
       </c>
       <c r="AP2">
-        <v>-0</v>
+        <v>0.834426468444833</v>
       </c>
     </row>
     <row r="3">
@@ -662,78 +689,200 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Atlas Lithium Corporation (NasdaqCM:ATLX)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Precious Metals</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>-0.5679999999999999</v>
+      </c>
+      <c r="G3">
+        <v>-5490</v>
+      </c>
+      <c r="H3">
+        <v>-5490</v>
+      </c>
+      <c r="I3">
+        <v>-26800</v>
+      </c>
+      <c r="J3">
+        <v>-26800</v>
+      </c>
+      <c r="K3">
+        <v>-26.6</v>
+      </c>
+      <c r="L3">
+        <v>-26600</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>22.9</v>
+      </c>
+      <c r="V3">
+        <v>0.06582351250359299</v>
+      </c>
+      <c r="W3">
+        <v>-22.35294117647059</v>
+      </c>
+      <c r="X3">
+        <v>0.1319741298819643</v>
+      </c>
+      <c r="Y3">
+        <v>-22.48491530635255</v>
+      </c>
+      <c r="Z3">
+        <v>0.001270648030495553</v>
+      </c>
+      <c r="AA3">
+        <v>-34.05336721728082</v>
+      </c>
+      <c r="AB3">
+        <v>0.1319741298819643</v>
+      </c>
+      <c r="AC3">
+        <v>-34.18534134716278</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>-22.9</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.07046153846153845</v>
+      </c>
+      <c r="AK3">
+        <v>1.389563106796117</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>-0</v>
+      </c>
+      <c r="AP3">
+        <v>0.8544776119402985</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Jupiter Gold Corporation (OTCPK:JUPG.F)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Precious Metals</t>
         </is>
       </c>
-      <c r="K3">
-        <v>-0.548</v>
-      </c>
-      <c r="M3">
-        <v>-0</v>
-      </c>
-      <c r="N3">
-        <v>-0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>-0</v>
-      </c>
-      <c r="Q3">
-        <v>-0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0.1613807534905092</v>
-      </c>
-      <c r="AB3">
-        <v>0.1613807534905092</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>-0</v>
-      </c>
-      <c r="AP3">
+      <c r="K4">
+        <v>-0.657</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0.1319741298819643</v>
+      </c>
+      <c r="AB4">
+        <v>0.1319741298819643</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
+      </c>
+      <c r="AP4">
         <v>-0</v>
       </c>
     </row>
